--- a/application/assets/excel/rekap_rencana_pengadaan.xlsx
+++ b/application/assets/excel/rekap_rencana_pengadaan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\noval\application\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6FFDE1D-06D8-4A69-991B-2A5F82B125C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8915EB16-4ABC-42C9-A2B8-9C428A76A907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E7A15CC7-3E23-4118-92B5-661F9C474EDE}"/>
   </bookViews>
@@ -57,10 +57,10 @@
     <t>Admin</t>
   </si>
   <si>
-    <t>Laporan Rencana Pengadaan</t>
-  </si>
-  <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Rekap Rencana Pengadaan</t>
   </si>
 </sst>
 </file>
@@ -112,13 +112,13 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -439,72 +439,72 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="33" style="3" customWidth="1"/>
-    <col min="5" max="5" width="37.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12" style="3" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="5.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="33" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
-    <row r="5" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
